--- a/data/sxbet/ligas/Champions League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Champions League_UEFA/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,26 +531,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x706deec51cdaeaab10697d88345a9605e2ae741f8edd315f86f49711040c8676</t>
+          <t>0xf0e6cbd21e0194dcb37f4957b04fb677e5f7ee9f8d40616fcde455b6f5f227f6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>26</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.5437</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.0637</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
@@ -559,52 +563,62 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb vs FC Thun</t>
+          <t>Gornik Zabrze vs Fenerbahçe</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FC Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
+          <t>0x9554ca4061faee131e0027895c6052c12ffc99028dbdbdc0cbaed34b84f83d72</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19582472</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
+          <t>L19558552</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1784986094</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1785261600</v>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1785060516</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1785348000</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>48.570225</t>
+          <t>59.764706</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -612,32 +626,48 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x818006fcbf26203fc601ff3e676bf292c22f9ba94bae860b73fd65385461ef8a</t>
+          <t>0x353715e3f6769b2d2de1f65c261527faebaeb9af3cda531b5bb2fb93023e5e7f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>63</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.8762</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>35.88794</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.1187</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FC Iberia 1999</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -645,52 +675,62 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NK CM Celje vs Egnatia Rrogozhine</t>
+          <t>SK Slovan Bratislava vs FC Iberia 1999</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>NK CM Celje</t>
+          <t>SK Slovan Bratislava</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhine</t>
+          <t>FC Iberia 1999</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x4af948b088509c74b8501ef2371ac69aca2e07ef27aaa518441f00bee5779150</t>
+          <t>0xaa78b65b4b857ef065f48dbcb39dcff19460b194305cbcf7f5e400377bb73e5b</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19557268</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
+          <t>L19559490</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1784980261</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1785262500</v>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1785059431</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1785348900</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>72.72727</t>
+          <t>302.214232</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -698,31 +738,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x665b369f4725c845e639d370e97e2cb4fe410dc123be3b585b3f180878564301</t>
+          <t>0x279b29ce10219e7b70680b5d12018ddfda7a2c4f6dd4f3a8674862ac2f090663</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.165</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>23.78</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
@@ -731,52 +779,62 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
+          <t>NK CM Celje vs Egnatia Rrogozhine</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps FC</t>
+          <t>NK CM Celje</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Mjallby AIF</t>
+          <t>Egnatia Rrogozhine</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x1899c9b65cff067e61565bfe09b869011a6687eb6d3269f60d67e143e6cd9e43</t>
+          <t>0xf3264b5069245a4bef486698d285e492665f8fd42ce62f75db076ef0d610b3c8</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19577122</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
+          <t>L19557268</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1784977413</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1785254400</v>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1785056092</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1785262500</t>
+        </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.209576</t>
+          <t>158.533333</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -784,31 +842,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x91d87c102b052c5391dfa63fc7dcd348a62beaa901beeb8b8a768bf60fb4a5bf</t>
+          <t>0x755e81bb5784d7b3c9e6486ea19b8ffe7212fad6e6c0cb843cb069a26e6eec88</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.4612</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>72.77</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
@@ -840,29 +906,39 @@
           <t>L19582472</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1784900105</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1785261600</v>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1785055626</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>22.088152</t>
+          <t>132.309091</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -870,31 +946,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x82ddad23a248269e2b8bf84351c8d266cf1f11c116b642f5d84c06741c7a0619</t>
+          <t>0xe8917320e1c802fce77dabd400fa7cd1e5ef36dcfd4bf42b42bd14dbe990b3eb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>13</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.745</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>69.73</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.375</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
@@ -903,52 +987,62 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva vs Víkingur Reykjavík</t>
+          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Lincoln Red Imps FC</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Mjallby AIF</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x962034a21eaa515d702829db03261f0b9ed39343dc7f36c744b170d7ebded7df</t>
+          <t>0x7c1e209322509ecf8a1b23dbc33db4cc7e79d00f2aef5b680bf0c7fff9fd4bfe</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19577307</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
+          <t>L19577122</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1784897170</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1785346200</v>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1785047610</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1785254400</t>
+        </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>18.470577</t>
+          <t>185.946667</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -956,31 +1050,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x8ab075f26d4fb133b3e569ea98af30f848d71683db604eab453ad0b60dca85e8</t>
+          <t>0x88e2378f5a143c7db391bb289784efb444eb47a5c1bc9793a6f9c4b6bd837f8e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>30</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.8037</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.1387</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
@@ -989,52 +1091,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Lech Poznan vs Aarhus AGF</t>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>GNK Dinamo Zagreb</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Aarhus AGF</t>
+          <t>FC Thun</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x32b28c80c59c8961ad85019af9cdf99d3f078d598185e71cd8abb27700f16ba2</t>
+          <t>0xebe3cd111a752d967882212fb73e0971d278b9b69d59c03364b97d883c138d02</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19558561</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1784895629</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1785344400</v>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1785044121</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37.706998</t>
+          <t>198.414414</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1042,32 +1154,48 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x76babde97bbe6342118533f3f3ad50e6e224fc6fd940aeca0e905d6733dd5175</t>
+          <t>0x61cde0937a84685bfdbd9e98f6a7e8a0cc4f1889f6665e9bb4792104f7ec7ea5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>26</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.3775</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.1087</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FC Iberia 1999</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -1075,52 +1203,62 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb vs FC Thun</t>
+          <t>SK Slovan Bratislava vs FC Iberia 1999</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb</t>
+          <t>SK Slovan Bratislava</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>FC Thun</t>
+          <t>FC Iberia 1999</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xe9d1eec91edb87730b0815143321f5ff812a64bbf914f9153fe49b15d31bee20</t>
+          <t>0xaa78b65b4b857ef065f48dbcb39dcff19460b194305cbcf7f5e400377bb73e5b</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19582472</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
+          <t>L19559490</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1784893721</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1785261600</v>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1785041778</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1785348900</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>70.554199</t>
+          <t>31.08046</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1128,31 +1266,39 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xee16c529f939026c958e6ddc04bce23b68a2e098ed10911de866ebc5ffd04d1e</t>
+          <t>0xb9423aefda3378641faef962e9aea7b3ce3a4217b1489c22188fbd378d6e0a13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.445</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>132.48</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
@@ -1161,52 +1307,62 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Lincoln Red Imps FC</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>Mjallby AIF</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x74fee38d896acdfb079a1d86f4347878d621fd4f0d8ac4b06615bc723fc48acf</t>
+          <t>0x7c1e209322509ecf8a1b23dbc33db4cc7e79d00f2aef5b680bf0c7fff9fd4bfe</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19563379</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
+          <t>L19577122</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1784890462</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1785264300</v>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1785041402</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1785254400</t>
+        </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.801798</t>
+          <t>358.054054</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1214,17 +1370,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xfc0b2e1db9ca0ccfd7931bdb66c1ba6d7d6524d378b965ea8bd5bd0331f7b869</t>
+          <t>0x7546990f5105879a6f4070af0c207deb23e089f9cd6d741088af685eb818e923</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
+          <t>0x52e769B148C8472a973EcFC9FFC0Cd8A6eE913ea</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1232,14 +1392,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>138</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1.4663</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.5725</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lech Poznan</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -1247,52 +1419,62 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+          <t>Lech Poznan vs Aarhus AGF</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>Aarhus AGF</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x74fee38d896acdfb079a1d86f4347878d621fd4f0d8ac4b06615bc723fc48acf</t>
+          <t>0x32020c9af56171026f9ca25f333b0c8fbc5c646597d73682de252484ad127d27</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19563379</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
+          <t>L19558561</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1784890461</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1785264300</v>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1785033197</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1785344400</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>296.136129</t>
+          <t>1.746725</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1300,17 +1482,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xf235c34c6db10b5456e39c6710ed412f8ffab1d22b3daa85a7ca0e19a8424b7c</t>
+          <t>0xaa31bee9619141709dddf44c2b00632e6fc62aeb3e57043d7a0cfef7c1732015</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1318,14 +1504,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>128</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.4663</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.4675</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb -1.5</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -1333,52 +1531,62 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>GNK Dinamo Zagreb</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>FC Thun</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x74fee38d896acdfb079a1d86f4347878d621fd4f0d8ac4b06615bc723fc48acf</t>
+          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19563379</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1784890332</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1785264300</v>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1785012663</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>275.209694</t>
+          <t>2.139037</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1386,17 +1594,21 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x392d99c071c44b52b3d23bdf086278e82837c3330125a1e832527d6a6cabfcbb</t>
+          <t>0x706deec51cdaeaab10697d88345a9605e2ae741f8edd315f86f49711040c8676</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1404,14 +1616,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>26</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.6125</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>22.16017</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.4563</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb -1.5</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -1419,52 +1643,62 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>GNK Dinamo Zagreb</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>FC Thun</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x6f059f958a714458632f78aafc6e1d15b2de9ff3fa0b4734fc30b4380a4d1054</t>
+          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19563379</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1784889212</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1785264300</v>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1784986094</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>43.493878</t>
+          <t>48.570236</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1472,32 +1706,48 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x53445b69be8e1164f5c419a71c3c3a9cfd9c3aff9d05959df0e841723394a1b3</t>
+          <t>0x818006fcbf26203fc601ff3e676bf292c22f9ba94bae860b73fd65385461ef8a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xe2C68b7ef85645e47F9b94382c3Db59b046945a2</t>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>28</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.7837</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.1238</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Egnatia Rrogozhine</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -1505,52 +1755,62 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Lech Poznan vs Aarhus AGF</t>
+          <t>NK CM Celje vs Egnatia Rrogozhine</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>NK CM Celje</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Aarhus AGF</t>
+          <t>Egnatia Rrogozhine</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x32b28c80c59c8961ad85019af9cdf99d3f078d598185e71cd8abb27700f16ba2</t>
+          <t>0x4af948b088509c74b8501ef2371ac69aca2e07ef27aaa518441f00bee5779150</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19558561</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
+          <t>L19557268</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1784888665</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1785344400</v>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1784980261</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1785262500</t>
+        </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>36.485537</t>
+          <t>72.727273</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1558,12 +1818,16 @@
           <t>SXR</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x7c3fff1d3b6a87feec1182ab499530ed5f2c0c3c6518142053a93d1426386836</t>
+          <t>0x665b369f4725c845e639d370e97e2cb4fe410dc123be3b585b3f180878564301</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1571,18 +1835,22 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>24</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.4988</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.835</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
@@ -1591,60 +1859,1154 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Mjallby AIF</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x1899c9b65cff067e61565bfe09b869011a6687eb6d3269f60d67e143e6cd9e43</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19577122</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1784977413</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1785254400</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1.209581</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0x91d87c102b052c5391dfa63fc7dcd348a62beaa901beeb8b8a768bf60fb4a5bf</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.5387</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1784900105</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>22.088167</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0x82ddad23a248269e2b8bf84351c8d266cf1f11c116b642f5d84c06741c7a0619</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.255</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Hapoel Be'er Sheva vs Víkingur Reykjavík</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Hapoel Be'er Sheva</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Víkingur Reykjavík</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x962034a21eaa515d702829db03261f0b9ed39343dc7f36c744b170d7ebded7df</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19577307</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1784897170</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1785346200</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>18.470588</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0x8ab075f26d4fb133b3e569ea98af30f848d71683db604eab453ad0b60dca85e8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.1963</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Lech Poznan vs Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Lech Poznan</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x32b28c80c59c8961ad85019af9cdf99d3f078d598185e71cd8abb27700f16ba2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19558561</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1784895629</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1785344400</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>37.707006</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0x76babde97bbe6342118533f3f3ad50e6e224fc6fd940aeca0e905d6733dd5175</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>43.91999</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.6225</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb -1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0xe9d1eec91edb87730b0815143321f5ff812a64bbf914f9153fe49b15d31bee20</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1784893721</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>70.554201</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0xee16c529f939026c958e6ddc04bce23b68a2e098ed10911de866ebc5ffd04d1e</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0x74fee38d896acdfb079a1d86f4347878d621fd4f0d8ac4b06615bc723fc48acf</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19563379</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1784890462</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1785264300</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1.801802</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0xfc0b2e1db9ca0ccfd7931bdb66c1ba6d7d6524d378b965ea8bd5bd0331f7b869</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>158.06266</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.5337</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0x74fee38d896acdfb079a1d86f4347878d621fd4f0d8ac4b06615bc723fc48acf</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19563379</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1784890461</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1785264300</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>296.136131</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0xf235c34c6db10b5456e39c6710ed412f8ffab1d22b3daa85a7ca0e19a8424b7c</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>146.89318</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.5337</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x74fee38d896acdfb079a1d86f4347878d621fd4f0d8ac4b06615bc723fc48acf</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19563379</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1784890332</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1785264300</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>275.209705</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0x392d99c071c44b52b3d23bdf086278e82837c3330125a1e832527d6a6cabfcbb</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>16.85388</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.3875</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0x6f059f958a714458632f78aafc6e1d15b2de9ff3fa0b4734fc30b4380a4d1054</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19563379</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1784889212</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1785264300</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>43.493884</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0x53445b69be8e1164f5c419a71c3c3a9cfd9c3aff9d05959df0e841723394a1b3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>7.89</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Lech Poznan vs Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Lech Poznan</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x32b28c80c59c8961ad85019af9cdf99d3f078d598185e71cd8abb27700f16ba2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19558561</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1784888665</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1785344400</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>36.485549</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0x7c3fff1d3b6a87feec1182ab499530ed5f2c0c3c6518142053a93d1426386836</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>24.56</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.5012</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CS U Craiova</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>CS U Craiova vs Levski Sofia</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>CS U Craiova</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Levski Sofia</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>0xf144a86466d7bb9112d98e7107394a1b2b9e20844f05baa80656f79674578a59</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>L19566703</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1784888647</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1785346200</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>48.997494</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1784888647</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1785346200</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>48.997506</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/sxbet/ligas/Champions League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Champions League_UEFA/trades.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xf0e6cbd21e0194dcb37f4957b04fb677e5f7ee9f8d40616fcde455b6f5f227f6</t>
+          <t>0x8fca93b88bb701783ff41ab50f088e43ecef252c16331853de0b5caaf82981ce</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,15 +539,19 @@
           <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>16.67317</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.0637</t>
+          <t>1.9525</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>Under/Over (0.5)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785060516</t>
+          <t>1785065229</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>59.764706</t>
+          <t>17.50464</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,39 +643,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x353715e3f6769b2d2de1f65c261527faebaeb9af3cda531b5bb2fb93023e5e7f</t>
+          <t>0xf0e6cbd21e0194dcb37f4957b04fb677e5f7ee9f8d40616fcde455b6f5f227f6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.88794</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.1187</t>
+          <t>1.0637</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>FC Iberia 1999</t>
-        </is>
-      </c>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -675,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SK Slovan Bratislava vs FC Iberia 1999</t>
+          <t>Gornik Zabrze vs Fenerbahçe</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>SK Slovan Bratislava</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>FC Iberia 1999</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xaa78b65b4b857ef065f48dbcb39dcff19460b194305cbcf7f5e400377bb73e5b</t>
+          <t>0x9554ca4061faee131e0027895c6052c12ffc99028dbdbdc0cbaed34b84f83d72</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19559490</t>
+          <t>L19558552</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785059431</t>
+          <t>1785060516</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785348900</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>302.214232</t>
+          <t>59.764706</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,31 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x279b29ce10219e7b70680b5d12018ddfda7a2c4f6dd4f3a8674862ac2f090663</t>
+          <t>0x353715e3f6769b2d2de1f65c261527faebaeb9af3cda531b5bb2fb93023e5e7f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>35.88794</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.1187</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Champions League</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FC Iberia 1999</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -779,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NK CM Celje vs Egnatia Rrogozhine</t>
+          <t>SK Slovan Bratislava vs FC Iberia 1999</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>NK CM Celje</t>
+          <t>SK Slovan Bratislava</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhine</t>
+          <t>FC Iberia 1999</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xf3264b5069245a4bef486698d285e492665f8fd42ce62f75db076ef0d610b3c8</t>
+          <t>0xaa78b65b4b857ef065f48dbcb39dcff19460b194305cbcf7f5e400377bb73e5b</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19557268</t>
+          <t>L19559490</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785056092</t>
+          <t>1785059431</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785262500</t>
+          <t>1785348900</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>158.533333</t>
+          <t>302.214232</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,28 +859,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x755e81bb5784d7b3c9e6486ea19b8ffe7212fad6e6c0cb843cb069a26e6eec88</t>
+          <t>0x279b29ce10219e7b70680b5d12018ddfda7a2c4f6dd4f3a8674862ac2f090663</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>72.77</t>
+          <t>23.78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -883,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb vs FC Thun</t>
+          <t>NK CM Celje vs Egnatia Rrogozhine</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb</t>
+          <t>NK CM Celje</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FC Thun</t>
+          <t>Egnatia Rrogozhine</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
+          <t>0xf3264b5069245a4bef486698d285e492665f8fd42ce62f75db076ef0d610b3c8</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19582472</t>
+          <t>L19557268</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785055626</t>
+          <t>1785056092</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785262500</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>132.309091</t>
+          <t>158.533333</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xe8917320e1c802fce77dabd400fa7cd1e5ef36dcfd4bf42b42bd14dbe990b3eb</t>
+          <t>0x755e81bb5784d7b3c9e6486ea19b8ffe7212fad6e6c0cb843cb069a26e6eec88</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -966,17 +974,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>69.73</t>
+          <t>72.77</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -987,27 +995,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps FC</t>
+          <t>GNK Dinamo Zagreb</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Mjallby AIF</t>
+          <t>FC Thun</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x7c1e209322509ecf8a1b23dbc33db4cc7e79d00f2aef5b680bf0c7fff9fd4bfe</t>
+          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19577122</t>
+          <t>L19582472</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1032,17 +1040,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785047610</t>
+          <t>1785055626</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785254400</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>185.946667</t>
+          <t>132.309091</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,28 +1067,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x88e2378f5a143c7db391bb289784efb444eb47a5c1bc9793a6f9c4b6bd837f8e</t>
+          <t>0xe8917320e1c802fce77dabd400fa7cd1e5ef36dcfd4bf42b42bd14dbe990b3eb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>69.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.375</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1091,27 +1099,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb vs FC Thun</t>
+          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb</t>
+          <t>Lincoln Red Imps FC</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>FC Thun</t>
+          <t>Mjallby AIF</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xebe3cd111a752d967882212fb73e0971d278b9b69d59c03364b97d883c138d02</t>
+          <t>0x7c1e209322509ecf8a1b23dbc33db4cc7e79d00f2aef5b680bf0c7fff9fd4bfe</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19582472</t>
+          <t>L19577122</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1136,17 +1144,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785044121</t>
+          <t>1785047610</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785254400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>198.414414</t>
+          <t>185.946667</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,39 +1171,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x61cde0937a84685bfdbd9e98f6a7e8a0cc4f1889f6665e9bb4792104f7ec7ea5</t>
+          <t>0x88e2378f5a143c7db391bb289784efb444eb47a5c1bc9793a6f9c4b6bd837f8e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>27.53</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.1087</t>
+          <t>1.1387</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>FC Iberia 1999</t>
-        </is>
-      </c>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -1203,27 +1203,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SK Slovan Bratislava vs FC Iberia 1999</t>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>SK Slovan Bratislava</t>
+          <t>GNK Dinamo Zagreb</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>FC Iberia 1999</t>
+          <t>FC Thun</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xaa78b65b4b857ef065f48dbcb39dcff19460b194305cbcf7f5e400377bb73e5b</t>
+          <t>0xebe3cd111a752d967882212fb73e0971d278b9b69d59c03364b97d883c138d02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19559490</t>
+          <t>L19582472</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1248,17 +1248,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785041778</t>
+          <t>1785044121</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785348900</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>31.08046</t>
+          <t>198.414414</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,23 +1275,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xb9423aefda3378641faef962e9aea7b3ce3a4217b1489c22188fbd378d6e0a13</t>
+          <t>0x61cde0937a84685bfdbd9e98f6a7e8a0cc4f1889f6665e9bb4792104f7ec7ea5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>132.48</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.1087</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1299,7 +1303,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FC Iberia 1999</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -1307,27 +1315,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
+          <t>SK Slovan Bratislava vs FC Iberia 1999</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps FC</t>
+          <t>SK Slovan Bratislava</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Mjallby AIF</t>
+          <t>FC Iberia 1999</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x7c1e209322509ecf8a1b23dbc33db4cc7e79d00f2aef5b680bf0c7fff9fd4bfe</t>
+          <t>0xaa78b65b4b857ef065f48dbcb39dcff19460b194305cbcf7f5e400377bb73e5b</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19577122</t>
+          <t>L19559490</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1352,17 +1360,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785041402</t>
+          <t>1785041778</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785254400</t>
+          <t>1785348900</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>358.054054</t>
+          <t>31.08046</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,27 +1387,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x7546990f5105879a6f4070af0c207deb23e089f9cd6d741088af685eb818e923</t>
+          <t>0xb9423aefda3378641faef962e9aea7b3ce3a4217b1489c22188fbd378d6e0a13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x52e769B148C8472a973EcFC9FFC0Cd8A6eE913ea</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>132.48</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5725</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1407,11 +1411,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Lech Poznan</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -1419,27 +1419,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Lech Poznan vs Aarhus AGF</t>
+          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Lincoln Red Imps FC</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Aarhus AGF</t>
+          <t>Mjallby AIF</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x32020c9af56171026f9ca25f333b0c8fbc5c646597d73682de252484ad127d27</t>
+          <t>0x7c1e209322509ecf8a1b23dbc33db4cc7e79d00f2aef5b680bf0c7fff9fd4bfe</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19558561</t>
+          <t>L19577122</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1464,17 +1464,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785033197</t>
+          <t>1785041402</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785344400</t>
+          <t>1785254400</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.746725</t>
+          <t>358.054054</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,12 +1491,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xaa31bee9619141709dddf44c2b00632e6fc62aeb3e57043d7a0cfef7c1732015</t>
+          <t>0x7546990f5105879a6f4070af0c207deb23e089f9cd6d741088af685eb818e923</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
+          <t>0x52e769B148C8472a973EcFC9FFC0Cd8A6eE913ea</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.5725</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb -1.5</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb vs FC Thun</t>
+          <t>Lech Poznan vs Aarhus AGF</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>FC Thun</t>
+          <t>Aarhus AGF</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
+          <t>0x32020c9af56171026f9ca25f333b0c8fbc5c646597d73682de252484ad127d27</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19582472</t>
+          <t>L19558561</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785012663</t>
+          <t>1785033197</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785344400</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.139037</t>
+          <t>1.746725</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,12 +1603,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x706deec51cdaeaab10697d88345a9605e2ae741f8edd315f86f49711040c8676</t>
+          <t>0xaa31bee9619141709dddf44c2b00632e6fc62aeb3e57043d7a0cfef7c1732015</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1618,12 +1618,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22.16017</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4563</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1784986094</t>
+          <t>1785012663</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>48.570236</t>
+          <t>2.139037</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,12 +1715,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x818006fcbf26203fc601ff3e676bf292c22f9ba94bae860b73fd65385461ef8a</t>
+          <t>0x706deec51cdaeaab10697d88345a9605e2ae741f8edd315f86f49711040c8676</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22.16017</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.1238</t>
+          <t>1.4563</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhine</t>
+          <t>GNK Dinamo Zagreb -1.5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1755,27 +1755,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NK CM Celje vs Egnatia Rrogozhine</t>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>NK CM Celje</t>
+          <t>GNK Dinamo Zagreb</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhine</t>
+          <t>FC Thun</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x4af948b088509c74b8501ef2371ac69aca2e07ef27aaa518441f00bee5779150</t>
+          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19557268</t>
+          <t>L19582472</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1784980261</t>
+          <t>1784986094</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785262500</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>72.727273</t>
+          <t>48.570236</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1827,23 +1827,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x665b369f4725c845e639d370e97e2cb4fe410dc123be3b585b3f180878564301</t>
+          <t>0x818006fcbf26203fc601ff3e676bf292c22f9ba94bae860b73fd65385461ef8a</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.835</t>
+          <t>1.1238</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1851,7 +1855,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Egnatia Rrogozhine</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -1859,27 +1867,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
+          <t>NK CM Celje vs Egnatia Rrogozhine</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps FC</t>
+          <t>NK CM Celje</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Mjallby AIF</t>
+          <t>Egnatia Rrogozhine</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x1899c9b65cff067e61565bfe09b869011a6687eb6d3269f60d67e143e6cd9e43</t>
+          <t>0x4af948b088509c74b8501ef2371ac69aca2e07ef27aaa518441f00bee5779150</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19577122</t>
+          <t>L19557268</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1904,17 +1912,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1784977413</t>
+          <t>1784980261</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785254400</t>
+          <t>1785262500</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.209581</t>
+          <t>72.727273</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1931,7 +1939,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x91d87c102b052c5391dfa63fc7dcd348a62beaa901beeb8b8a768bf60fb4a5bf</t>
+          <t>0x665b369f4725c845e639d370e97e2cb4fe410dc123be3b585b3f180878564301</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1942,17 +1950,17 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.835</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1963,27 +1971,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb vs FC Thun</t>
+          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb</t>
+          <t>Lincoln Red Imps FC</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>FC Thun</t>
+          <t>Mjallby AIF</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
+          <t>0x1899c9b65cff067e61565bfe09b869011a6687eb6d3269f60d67e143e6cd9e43</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19582472</t>
+          <t>L19577122</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2008,17 +2016,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1784900105</t>
+          <t>1784977413</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785254400</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>22.088167</t>
+          <t>1.209581</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,7 +2043,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x82ddad23a248269e2b8bf84351c8d266cf1f11c116b642f5d84c06741c7a0619</t>
+          <t>0x91d87c102b052c5391dfa63fc7dcd348a62beaa901beeb8b8a768bf60fb4a5bf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2043,31 +2051,23 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -2075,27 +2075,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva vs Víkingur Reykjavík</t>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>GNK Dinamo Zagreb</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>FC Thun</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x962034a21eaa515d702829db03261f0b9ed39343dc7f36c744b170d7ebded7df</t>
+          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19577307</t>
+          <t>L19582472</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1784897170</t>
+          <t>1784900105</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785346200</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>18.470588</t>
+          <t>22.088167</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,12 +2147,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x8ab075f26d4fb133b3e569ea98af30f848d71683db604eab453ad0b60dca85e8</t>
+          <t>0x82ddad23a248269e2b8bf84351c8d266cf1f11c116b642f5d84c06741c7a0619</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.1963</t>
+          <t>1.255</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Aarhus AGF</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2187,27 +2187,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Lech Poznan vs Aarhus AGF</t>
+          <t>Hapoel Be'er Sheva vs Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Aarhus AGF</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x32b28c80c59c8961ad85019af9cdf99d3f078d598185e71cd8abb27700f16ba2</t>
+          <t>0x962034a21eaa515d702829db03261f0b9ed39343dc7f36c744b170d7ebded7df</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19558561</t>
+          <t>L19577307</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1784895629</t>
+          <t>1784897170</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785344400</t>
+          <t>1785346200</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>37.707006</t>
+          <t>18.470588</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x76babde97bbe6342118533f3f3ad50e6e224fc6fd940aeca0e905d6733dd5175</t>
+          <t>0x8ab075f26d4fb133b3e569ea98af30f848d71683db604eab453ad0b60dca85e8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2274,22 +2274,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>43.91999</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.1963</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb -1</t>
+          <t>Aarhus AGF</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2299,27 +2299,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb vs FC Thun</t>
+          <t>Lech Poznan vs Aarhus AGF</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>FC Thun</t>
+          <t>Aarhus AGF</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xe9d1eec91edb87730b0815143321f5ff812a64bbf914f9153fe49b15d31bee20</t>
+          <t>0x32b28c80c59c8961ad85019af9cdf99d3f078d598185e71cd8abb27700f16ba2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19582472</t>
+          <t>L19558561</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2344,17 +2344,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1784893721</t>
+          <t>1784895629</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785344400</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>70.554201</t>
+          <t>37.707006</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,31 +2371,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xee16c529f939026c958e6ddc04bce23b68a2e098ed10911de866ebc5ffd04d1e</t>
+          <t>0x76babde97bbe6342118533f3f3ad50e6e224fc6fd940aeca0e905d6733dd5175</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>43.91999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb -1</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -2403,27 +2411,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>GNK Dinamo Zagreb</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>FC Thun</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x74fee38d896acdfb079a1d86f4347878d621fd4f0d8ac4b06615bc723fc48acf</t>
+          <t>0xe9d1eec91edb87730b0815143321f5ff812a64bbf914f9153fe49b15d31bee20</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19563379</t>
+          <t>L19582472</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2448,17 +2456,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1784890462</t>
+          <t>1784893721</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785264300</t>
+          <t>1785261600</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.801802</t>
+          <t>70.554201</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,7 +2483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xfc0b2e1db9ca0ccfd7931bdb66c1ba6d7d6524d378b965ea8bd5bd0331f7b869</t>
+          <t>0xee16c529f939026c958e6ddc04bce23b68a2e098ed10911de866ebc5ffd04d1e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2486,12 +2494,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>158.06266</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2552,7 +2560,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1784890461</t>
+          <t>1784890462</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2562,7 +2570,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>296.136131</t>
+          <t>1.801802</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2579,7 +2587,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xf235c34c6db10b5456e39c6710ed412f8ffab1d22b3daa85a7ca0e19a8424b7c</t>
+          <t>0xfc0b2e1db9ca0ccfd7931bdb66c1ba6d7d6524d378b965ea8bd5bd0331f7b869</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2590,7 +2598,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>146.89318</t>
+          <t>158.06266</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2656,7 +2664,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1784890332</t>
+          <t>1784890461</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2666,7 +2674,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>275.209705</t>
+          <t>296.136131</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,28 +2691,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x392d99c071c44b52b3d23bdf086278e82837c3330125a1e832527d6a6cabfcbb</t>
+          <t>0xf235c34c6db10b5456e39c6710ed412f8ffab1d22b3daa85a7ca0e19a8424b7c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16.85388</t>
+          <t>146.89318</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3875</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2730,7 +2738,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x6f059f958a714458632f78aafc6e1d15b2de9ff3fa0b4734fc30b4380a4d1054</t>
+          <t>0x74fee38d896acdfb079a1d86f4347878d621fd4f0d8ac4b06615bc723fc48acf</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2760,7 +2768,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1784889212</t>
+          <t>1784890332</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2770,7 +2778,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>43.493884</t>
+          <t>275.209705</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,39 +2795,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x53445b69be8e1164f5c419a71c3c3a9cfd9c3aff9d05959df0e841723394a1b3</t>
+          <t>0x392d99c071c44b52b3d23bdf086278e82837c3330125a1e832527d6a6cabfcbb</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>16.85388</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.3875</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Aarhus AGF</t>
-        </is>
-      </c>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -2827,27 +2827,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Lech Poznan vs Aarhus AGF</t>
+          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Aarhus AGF</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x32b28c80c59c8961ad85019af9cdf99d3f078d598185e71cd8abb27700f16ba2</t>
+          <t>0x6f059f958a714458632f78aafc6e1d15b2de9ff3fa0b4734fc30b4380a4d1054</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19558561</t>
+          <t>L19563379</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1784888665</t>
+          <t>1784889212</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785344400</t>
+          <t>1785264300</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>36.485549</t>
+          <t>43.493884</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,110 +2899,222 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>0x53445b69be8e1164f5c419a71c3c3a9cfd9c3aff9d05959df0e841723394a1b3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7.89</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Lech Poznan vs Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Lech Poznan</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0x32b28c80c59c8961ad85019af9cdf99d3f078d598185e71cd8abb27700f16ba2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19558561</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1784888665</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1785344400</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>36.485549</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>0x7c3fff1d3b6a87feec1182ab499530ed5f2c0c3c6518142053a93d1426386836</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>24.56</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>1.5012</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>CS U Craiova</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>CS U Craiova vs Levski Sofia</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>CS U Craiova</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Levski Sofia</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>0xf144a86466d7bb9112d98e7107394a1b2b9e20844f05baa80656f79674578a59</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>L19566703</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>1784888647</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>1785346200</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>48.997506</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Champions League_UEFA/trades.xlsx
+++ b/data/sxbet/ligas/Champions League_UEFA/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x8fca93b88bb701783ff41ab50f088e43ecef252c16331853de0b5caaf82981ce</t>
+          <t>0x63f4a94cbc605d5ceaf2d46b8e5b1b5a6f3f0f71d39f0bdc4e02571de20e520d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.67317</t>
+          <t>512.4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.9525</t>
+          <t>1.4712</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Gornik Zabrze +1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x9554ca4061faee131e0027895c6052c12ffc99028dbdbdc0cbaed34b84f83d72</t>
+          <t>0xadbdfec15185453d1de4e24e30ba5b976909c13ba09f6ad285081bc63af967d6</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785065229</t>
+          <t>1785165707</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>17.50464</t>
+          <t>1087.320955</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,28 +643,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xf0e6cbd21e0194dcb37f4957b04fb677e5f7ee9f8d40616fcde455b6f5f227f6</t>
+          <t>0x540151146ee3bcc403f1802ec073b096d397edfba4f33f0f7356e7f349c648a0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>7.72998</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.0637</t>
+          <t>1.7025</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -675,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Gornik Zabrze vs Fenerbahçe</t>
+          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Gornik Zabrze</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x9554ca4061faee131e0027895c6052c12ffc99028dbdbdc0cbaed34b84f83d72</t>
+          <t>0x9cc6b2d054a0c42053bc5ab19dc3ee88c18f725ebcd8efe28681db2174696410</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19558552</t>
+          <t>L19563379</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785060516</t>
+          <t>1785161688</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785348000</t>
+          <t>1785264300</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>59.764706</t>
+          <t>11.00353</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,39 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x353715e3f6769b2d2de1f65c261527faebaeb9af3cda531b5bb2fb93023e5e7f</t>
+          <t>0xb85f2930e993f82e91dd714c91d6aaed9f1e0132043222fddf9a4db380687f69</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>35.88794</t>
+          <t>51.98999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.1187</t>
+          <t>1.7025</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>FC Iberia 1999</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -787,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SK Slovan Bratislava vs FC Iberia 1999</t>
+          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SK Slovan Bratislava</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FC Iberia 1999</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xaa78b65b4b857ef065f48dbcb39dcff19460b194305cbcf7f5e400377bb73e5b</t>
+          <t>0x9cc6b2d054a0c42053bc5ab19dc3ee88c18f725ebcd8efe28681db2174696410</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19559490</t>
+          <t>L19563379</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785059431</t>
+          <t>1785161592</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785348900</t>
+          <t>1785264300</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>302.214232</t>
+          <t>74.007103</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,28 +851,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x279b29ce10219e7b70680b5d12018ddfda7a2c4f6dd4f3a8674862ac2f090663</t>
+          <t>0x1fc6794b35b3c0b5edefd91ac12cf47323f59bccaae1882f8ceadaeca59615ff</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.7025</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -891,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NK CM Celje vs Egnatia Rrogozhine</t>
+          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>NK CM Celje</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhine</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xf3264b5069245a4bef486698d285e492665f8fd42ce62f75db076ef0d610b3c8</t>
+          <t>0x9cc6b2d054a0c42053bc5ab19dc3ee88c18f725ebcd8efe28681db2174696410</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19557268</t>
+          <t>L19563379</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785056092</t>
+          <t>1785161564</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785262500</t>
+          <t>1785264300</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>158.533333</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,23 +955,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x755e81bb5784d7b3c9e6486ea19b8ffe7212fad6e6c0cb843cb069a26e6eec88</t>
+          <t>0x821789ec1a64bed84e6e8aa3781fe81d654624dbcea9a78bb02fbab72096d6a2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>72.77</t>
+          <t>77.27999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.7025</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -995,27 +987,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb vs FC Thun</t>
+          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>FC Thun</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
+          <t>0x9cc6b2d054a0c42053bc5ab19dc3ee88c18f725ebcd8efe28681db2174696410</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19582472</t>
+          <t>L19563379</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1032,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785055626</t>
+          <t>1785161536</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785264300</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>132.309091</t>
+          <t>110.007103</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,28 +1059,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xe8917320e1c802fce77dabd400fa7cd1e5ef36dcfd4bf42b42bd14dbe990b3eb</t>
+          <t>0xa97709e82d14315c432e21254def497fd1f0ebd2a6879d54dfc8688666ccc774</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>69.73</t>
+          <t>36.70999</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.7025</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1099,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
+          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps FC</t>
+          <t>Heart of Midlothian</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Mjallby AIF</t>
+          <t>SK Puntigamer Sturm Graz</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x7c1e209322509ecf8a1b23dbc33db4cc7e79d00f2aef5b680bf0c7fff9fd4bfe</t>
+          <t>0x9cc6b2d054a0c42053bc5ab19dc3ee88c18f725ebcd8efe28681db2174696410</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19577122</t>
+          <t>L19563379</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1144,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785047610</t>
+          <t>1785161502</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785254400</t>
+          <t>1785264300</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>185.946667</t>
+          <t>52.256214</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,28 +1163,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x88e2378f5a143c7db391bb289784efb444eb47a5c1bc9793a6f9c4b6bd837f8e</t>
+          <t>0x7850fbdfa7c67fd010eb79aa79ef6b0bdaf4903d7abe0b055121a1a33b465c45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>2.25181</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.1387</t>
+          <t>1.7612</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1203,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb vs FC Thun</t>
+          <t>Shamrock Rovers vs FC Ararat-Armenia</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>FC Thun</t>
+          <t>FC Ararat-Armenia</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xebe3cd111a752d967882212fb73e0971d278b9b69d59c03364b97d883c138d02</t>
+          <t>0x1216b3e173055248b35c952e70629973fc1b59ea372339b454c1490c4874559f</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19582472</t>
+          <t>L19583825</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1248,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785044121</t>
+          <t>1785161323</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785265200</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>198.414414</t>
+          <t>2.958043</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,12 +1267,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x61cde0937a84685bfdbd9e98f6a7e8a0cc4f1889f6665e9bb4792104f7ec7ea5</t>
+          <t>0xb8c9a175a0a59698da3a03d9ebaad14bac0b9fa517b0e991c5a2fbe5d227db5a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1290,22 +1282,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>87.79</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.1087</t>
+          <t>1.6863</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>FC Iberia 1999</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1315,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SK Slovan Bratislava vs FC Iberia 1999</t>
+          <t>Shamrock Rovers vs FC Ararat-Armenia</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SK Slovan Bratislava</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>FC Iberia 1999</t>
+          <t>FC Ararat-Armenia</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xaa78b65b4b857ef065f48dbcb39dcff19460b194305cbcf7f5e400377bb73e5b</t>
+          <t>0xf01c0c3ad882b1d7bc694c7b0dc22f28d64033f1dfd0f9399ca52d172a5396a0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19559490</t>
+          <t>L19583825</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1360,17 +1352,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785041778</t>
+          <t>1785160383</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785348900</t>
+          <t>1785265200</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>31.08046</t>
+          <t>127.92714</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,23 +1379,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xb9423aefda3378641faef962e9aea7b3ce3a4217b1489c22188fbd378d6e0a13</t>
+          <t>0x42159fbf09230e1f67df2b203c6bfc2c09726365be50c241488c13d8a1a53c1a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>132.48</t>
+          <t>237.68665</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.8738</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1419,27 +1411,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
+          <t>Gornik Zabrze vs Fenerbahçe</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps FC</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Mjallby AIF</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x7c1e209322509ecf8a1b23dbc33db4cc7e79d00f2aef5b680bf0c7fff9fd4bfe</t>
+          <t>0xef785f51e7bdaa78617ace0793d6bf45401b9d98babdf44677e3d66e8febafdb</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19577122</t>
+          <t>L19558552</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1464,17 +1456,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785041402</t>
+          <t>1785160190</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785254400</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>358.054054</t>
+          <t>272.030501</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,39 +1483,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x7546990f5105879a6f4070af0c207deb23e089f9cd6d741088af685eb818e923</t>
+          <t>0x2cbc733327cf9e03f57b4c8a3dcf1d86d2d6d3b6dfcbe91f91447946117bdc01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x52e769B148C8472a973EcFC9FFC0Cd8A6eE913ea</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24.34</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5725</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Lech Poznan</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -1531,27 +1515,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Lech Poznan vs Aarhus AGF</t>
+          <t>Shamrock Rovers vs FC Ararat-Armenia</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Aarhus AGF</t>
+          <t>FC Ararat-Armenia</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x32020c9af56171026f9ca25f333b0c8fbc5c646597d73682de252484ad127d27</t>
+          <t>0x4bcb1bf2ed3eff35878050222d0a04fe4fb1ae36e653317545c524dc62f71a71</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19558561</t>
+          <t>L19583825</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1576,17 +1560,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785033197</t>
+          <t>1785160000</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785344400</t>
+          <t>1785265200</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.746725</t>
+          <t>50.973822</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,12 +1587,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xaa31bee9619141709dddf44c2b00632e6fc62aeb3e57043d7a0cfef7c1732015</t>
+          <t>0x445f9eddd5f7e6efd784e11b4b818f936fad758c16e63ee5e320403fe80df87c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1618,22 +1602,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100.45</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb -1.5</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1643,27 +1627,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb vs FC Thun</t>
+          <t>KuPS vs Sabah Baku FK</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>FC Thun</t>
+          <t>Sabah Baku FK</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
+          <t>0x5fd787b906e955291cd9eff56f5cf694172dfcf192b7f120ff5bc27dd2425c40</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19582472</t>
+          <t>L19581643</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1688,17 +1672,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785012663</t>
+          <t>1785158085</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785250800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2.139037</t>
+          <t>149.646182</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,12 +1699,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x706deec51cdaeaab10697d88345a9605e2ae741f8edd315f86f49711040c8676</t>
+          <t>0x853386c2c429f25ff828f8a1560f2b9d702ea67e6841b5d7cab9e202d50eab10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1730,22 +1714,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>22.16017</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4563</t>
+          <t>1.4788</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb -1.5</t>
+          <t>Gornik Zabrze +1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1755,27 +1739,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb vs FC Thun</t>
+          <t>Gornik Zabrze vs Fenerbahçe</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>FC Thun</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
+          <t>0xadbdfec15185453d1de4e24e30ba5b976909c13ba09f6ad285081bc63af967d6</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19582472</t>
+          <t>L19558552</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1800,17 +1784,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1784986094</t>
+          <t>1785154572</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>48.570236</t>
+          <t>2.172324</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1827,39 +1811,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x818006fcbf26203fc601ff3e676bf292c22f9ba94bae860b73fd65385461ef8a</t>
+          <t>0x3834317523c856bd86acaf11bce5da56dcecd107e3fca8f0d8b28a9b32995888</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>163.13999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.1238</t>
+          <t>1.8137</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Egnatia Rrogozhine</t>
-        </is>
-      </c>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -1867,27 +1843,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>NK CM Celje vs Egnatia Rrogozhine</t>
+          <t>Gornik Zabrze vs Fenerbahçe</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>NK CM Celje</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhine</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x4af948b088509c74b8501ef2371ac69aca2e07ef27aaa518441f00bee5779150</t>
+          <t>0x8d9c6bf8d8b570263c7bff7d199972327800fdd14ff5fa5fe4973afd5942a1cc</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19557268</t>
+          <t>L19558552</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1912,17 +1888,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1784980261</t>
+          <t>1785154498</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785262500</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>72.727273</t>
+          <t>200.47925</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,31 +1915,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x665b369f4725c845e639d370e97e2cb4fe410dc123be3b585b3f180878564301</t>
+          <t>0x19ae83f18d0dabf971b19343088637425a85803623f21514447d7e60b45faa51</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>55.60999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.835</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -1971,27 +1955,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
+          <t>FC Kairat Almaty vs Omonia Nicosia</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps FC</t>
+          <t>FC Kairat Almaty</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Mjallby AIF</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x1899c9b65cff067e61565bfe09b869011a6687eb6d3269f60d67e143e6cd9e43</t>
+          <t>0xf1d0eb05b8634845bb22126689ae2b16ac42cafc2bff1ab20a53489a40befeea</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19577122</t>
+          <t>L19567340</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2016,17 +2000,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1784977413</t>
+          <t>1785154215</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785254400</t>
+          <t>1785337200</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.209581</t>
+          <t>92.87681</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,28 +2027,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x91d87c102b052c5391dfa63fc7dcd348a62beaa901beeb8b8a768bf60fb4a5bf</t>
+          <t>0xeab1ec01838702ceba5288cd7fb4a4ba1ac8e59e392eca217e3aa0509efa8ee0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>222.65</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.7862</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2075,27 +2059,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb vs FC Thun</t>
+          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb</t>
+          <t>Lincoln Red Imps FC</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>FC Thun</t>
+          <t>Mjallby AIF</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
+          <t>0x7e061b4630b822d04d4ce6936398d20dadf64b5f22b6e82afac12255418de44f</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19582472</t>
+          <t>L19577122</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2120,17 +2104,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1784900105</t>
+          <t>1785153903</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785254400</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>22.088167</t>
+          <t>283.17965</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,7 +2131,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x82ddad23a248269e2b8bf84351c8d266cf1f11c116b642f5d84c06741c7a0619</t>
+          <t>0x7a69a54ff0912151841e92e70f56d1c84728c1e2483d079931e2cf2a640483a4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2155,19 +2139,15 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>9.86988</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1.9463</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2175,11 +2155,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -2187,27 +2163,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva vs Víkingur Reykjavík</t>
+          <t>Crvena Zvezda vs Larne</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x962034a21eaa515d702829db03261f0b9ed39343dc7f36c744b170d7ebded7df</t>
+          <t>0x950df66650748641b3e682f6ec99b45d5f051afde9386ea269fd4e6fa1a4d4bb</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19577307</t>
+          <t>L19566868</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2232,17 +2208,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1784897170</t>
+          <t>1785152368</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785346200</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>18.470588</t>
+          <t>10.43052</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,27 +2235,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x8ab075f26d4fb133b3e569ea98af30f848d71683db604eab453ad0b60dca85e8</t>
+          <t>0x6e0a3ee8b141f9e25d6e4306ffddead6d9485b015635f20cd5de803ca49843a0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>231.81993</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.1963</t>
+          <t>1.9425</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2287,11 +2259,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Aarhus AGF</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -2299,27 +2267,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Lech Poznan vs Aarhus AGF</t>
+          <t>Crvena Zvezda vs Larne</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Aarhus AGF</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x32b28c80c59c8961ad85019af9cdf99d3f078d598185e71cd8abb27700f16ba2</t>
+          <t>0x950df66650748641b3e682f6ec99b45d5f051afde9386ea269fd4e6fa1a4d4bb</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19558561</t>
+          <t>L19566868</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2344,17 +2312,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1784895629</t>
+          <t>1785151878</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785344400</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>37.707006</t>
+          <t>245.96279</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,39 +2339,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x76babde97bbe6342118533f3f3ad50e6e224fc6fd940aeca0e905d6733dd5175</t>
+          <t>0xe51cdf9242ebac264c48a8ff9133b986adb1707e3d8a0796740c87931ecccd09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>43.91999</t>
+          <t>4.74988</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.9425</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>GNK Dinamo Zagreb -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
@@ -2411,27 +2371,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb vs FC Thun</t>
+          <t>Crvena Zvezda vs Larne</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>GNK Dinamo Zagreb</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>FC Thun</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xe9d1eec91edb87730b0815143321f5ff812a64bbf914f9153fe49b15d31bee20</t>
+          <t>0x950df66650748641b3e682f6ec99b45d5f051afde9386ea269fd4e6fa1a4d4bb</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19582472</t>
+          <t>L19566868</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2456,17 +2416,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1784893721</t>
+          <t>1785151869</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785261600</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>70.554201</t>
+          <t>5.03966</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2483,28 +2443,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xee16c529f939026c958e6ddc04bce23b68a2e098ed10911de866ebc5ffd04d1e</t>
+          <t>0x59413c04413d89fdebcd13958d0a1e0049e0258b323af9685d481c22722affc0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5.66997</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.8525</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2530,7 +2490,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x74fee38d896acdfb079a1d86f4347878d621fd4f0d8ac4b06615bc723fc48acf</t>
+          <t>0x8688192826219652c276c2eddcb21dbd8727df9b4ba1237eefbec4ee6e1b626d</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2560,7 +2520,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1784890462</t>
+          <t>1785150794</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2570,7 +2530,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.801802</t>
+          <t>6.650991</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2587,23 +2547,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xfc0b2e1db9ca0ccfd7931bdb66c1ba6d7d6524d378b965ea8bd5bd0331f7b869</t>
+          <t>0x12a6e08a96be5439987a31d520daf155979873e1f8ad5e8483d4fa838fe48493</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>158.06266</t>
+          <t>236.59989</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.9438</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2619,27 +2579,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+          <t>Crvena Zvezda vs Larne</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x74fee38d896acdfb079a1d86f4347878d621fd4f0d8ac4b06615bc723fc48acf</t>
+          <t>0x950df66650748641b3e682f6ec99b45d5f051afde9386ea269fd4e6fa1a4d4bb</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19563379</t>
+          <t>L19566868</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2664,17 +2624,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1784890461</t>
+          <t>1785150430</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785264300</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>296.136131</t>
+          <t>250.70187</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2691,23 +2651,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xf235c34c6db10b5456e39c6710ed412f8ffab1d22b3daa85a7ca0e19a8424b7c</t>
+          <t>0xf95ca4198383aadc6e52b54ee0bbeb8493bfdb07b08c533134b6aaf1fc018913</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>146.89318</t>
+          <t>235.66991</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2723,27 +2683,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+          <t>Crvena Zvezda vs Larne</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x74fee38d896acdfb079a1d86f4347878d621fd4f0d8ac4b06615bc723fc48acf</t>
+          <t>0x950df66650748641b3e682f6ec99b45d5f051afde9386ea269fd4e6fa1a4d4bb</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19563379</t>
+          <t>L19566868</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2768,17 +2728,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1784890332</t>
+          <t>1785150426</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785264300</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>275.209705</t>
+          <t>250.71267</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2795,28 +2755,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x392d99c071c44b52b3d23bdf086278e82837c3330125a1e832527d6a6cabfcbb</t>
+          <t>0xfc902fb97224ff9743764883e6fa8bbf519d1209a81947e4a4372ee0ed798641</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>16.85388</t>
+          <t>4.74998</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3875</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Champions League</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2827,27 +2787,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+          <t>Crvena Zvezda vs Larne</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Heart of Midlothian</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SK Puntigamer Sturm Graz</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x6f059f958a714458632f78aafc6e1d15b2de9ff3fa0b4734fc30b4380a4d1054</t>
+          <t>0x950df66650748641b3e682f6ec99b45d5f051afde9386ea269fd4e6fa1a4d4bb</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19563379</t>
+          <t>L19566868</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2872,17 +2832,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1784889212</t>
+          <t>1785150423</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785264300</t>
+          <t>1785348000</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>43.493884</t>
+          <t>5.05317</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,12 +2859,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x53445b69be8e1164f5c419a71c3c3a9cfd9c3aff9d05959df0e841723394a1b3</t>
+          <t>0x082fb97a907f72a50fdf7b2596969ba7e566f73aa560ef45941030072fe5371c</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2914,22 +2874,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.8413</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Champions League</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Aarhus AGF</t>
+          <t>NK CM Celje</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2939,27 +2899,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Lech Poznan vs Aarhus AGF</t>
+          <t>NK CM Celje vs Egnatia Rrogozhine</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>NK CM Celje</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Aarhus AGF</t>
+          <t>Egnatia Rrogozhine</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x32b28c80c59c8961ad85019af9cdf99d3f078d598185e71cd8abb27700f16ba2</t>
+          <t>0xf3264b5069245a4bef486698d285e492665f8fd42ce62f75db076ef0d610b3c8</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19558561</t>
+          <t>L19557268</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2984,17 +2944,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1784888665</t>
+          <t>1785150414</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785344400</t>
+          <t>1785262500</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>36.485549</t>
+          <t>126.169391</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3011,110 +2971,5942 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>0x5ed0e5abf67ebd3d849024e7834eee4b217e896d8aa98c848c5edca46a726264</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>134.07</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.9375</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda vs Larne</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Larne</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0x950df66650748641b3e682f6ec99b45d5f051afde9386ea269fd4e6fa1a4d4bb</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19566868</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1785150406</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1785348000</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>143.008</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0x4ec65d00043f9be09b82a761e1adeb0e3465b6d41091b3f214296c0a2be5a929</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>96.02</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.8125</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Gornik Zabrze vs Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Gornik Zabrze</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0x8d9c6bf8d8b570263c7bff7d199972327800fdd14ff5fa5fe4973afd5942a1cc</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19558552</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1785149729</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1785348000</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>118.178462</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0x8c9960bc5d787fa7831ca036a1018407d42c71b1c4ce758b2881e769e3d00e63</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1.03999</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.7163</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers vs FC Ararat-Armenia</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>FC Ararat-Armenia</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0xf5b560430b6d069f4b4b87ae62ea1c515e158b5d5b231948031852faa4bfa83f</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19583825</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1785149699</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1785265200</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1.451993</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0x9eabf5bb1988e87cb88e434d31001e6a58515d24eea4443f12531ae423f722f2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.3013</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers -1.5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers vs FC Ararat-Armenia</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>FC Ararat-Armenia</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0xf5b560430b6d069f4b4b87ae62ea1c515e158b5d5b231948031852faa4bfa83f</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19583825</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1785148867</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1785265200</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>38.174274</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0x3fc677cd12555675e7099ee8b60ae5ba63ddfd35288739532291a8645bda6ce9</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>191.06999</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.6887</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers vs FC Ararat-Armenia</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>FC Ararat-Armenia</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0xf01c0c3ad882b1d7bc694c7b0dc22f28d64033f1dfd0f9399ca52d172a5396a0</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19583825</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1785146196</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1785265200</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>277.415593</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0x469ee20543d1ec2556f12f2402e3727ce4236b961173efc567e99803ac718bf9</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>75.66999</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.6012</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty vs Omonia Nicosia</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Omonia Nicosia</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0xf1d0eb05b8634845bb22126689ae2b16ac42cafc2bff1ab20a53489a40befeea</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19567340</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1785146160</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1785337200</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>125.854453</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0xca54bcd6312fbe0adf0c0e33a0c2790b62de983e31dbfa81690400c173abba94</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>427.28998</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.7913</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Mjallby AIF</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0x7e061b4630b822d04d4ce6936398d20dadf64b5f22b6e82afac12255418de44f</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19577122</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1785146134</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1785254400</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>540.018932</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0xdafbcfd56f6eb0a56bf5d0c8ccf7ba67f66d4c690aa68829b34a5837d292c278</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0x26343cE07651A5C5C515ec7245F607C05b005d3e</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>10.35999</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.5012</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>KuPS vs Sabah Baku FK</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Sabah Baku FK</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0x93928c7c13a86cb15f048409d12d04f29076c1ee3901a18379c7f8a2324ea352</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19581643</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1785145189</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1785250800</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>20.668309</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0xc4bbfe8163b65430f679283b04d011de8ffbfb985f30c715d13d72fc7012567b</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x44cE278A4b373d2bFD26e6a2F5fA4E3550151d67</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4.59998</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.915</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda vs Larne</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Larne</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0x2d26cd20f1b572e31dc24d92bbb4220e1d8686376d97f645f5f4354b5ef9260f</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19566868</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1785144814</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1785348000</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>5.027301</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0xa743f5bcb94c779d91b925959856bffd99108bbfdac564ea07e007f9f969138f</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.465</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Kauno Zalgiris vs KÍ Klaksvík</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Kauno Zalgiris</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>KÍ Klaksvík</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0xfd44a2393475bf1ae8d42aefd200c50a503fe4d9dfc3930e7db69193123bfd53</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19566095</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1785144144</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1785340800</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2.258065</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x1c6bcb876ad777cac158fd5a9d6d6639b3184542996fe5d28e74eb1c27c20b0e</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.1638</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Mjallby AIF</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x19771660e7a4984ba9f2267f53439a0da3d4ab62381a1815918b7cd9673267bb</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19577122</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1785143209</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1785254400</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>6.167939</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0x09a8c1253e27c65c2ae3562d9cf5c87c459396d08687bde51a751960d7759d95</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>156.41999</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty vs Omonia Nicosia</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Omonia Nicosia</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0xf1d0eb05b8634845bb22126689ae2b16ac42cafc2bff1ab20a53489a40befeea</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19567340</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1785139256</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1785337200</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>256.426213</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x6ac1fbf7c9ed6b84d2a5073d38a6f406ca15cc0fe18c1eda5e2d0f2a4ff3fcb9</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>41.75999</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty 0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty vs Omonia Nicosia</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Omonia Nicosia</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x8edc16d764a11b28019e1c8667145b7c740b6a71d683108305dd23501aa331d8</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19567340</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1785139255</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1785337200</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>68.459</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0xda868acde920669947951482a1a41d9af6d50e62d509261ee85d7ac6a8f9c940</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SK Slovan Bratislava vs FC Iberia 1999</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>SK Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>FC Iberia 1999</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0xcf41308af20cedf972ab86d4583858eed5d6afd8468a8de2a70a53ca10c0910a</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19559490</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1785136376</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1785348900</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>6.097561</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0xeb27f154055bdad5ab97b4b8446d404e3378a325f30e0af9ed3f8bafc967ba62</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.4463</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda vs Larne</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Larne</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0xdbf1c093a28709935b76f299fab09b833d132f7b3948187a93486fc0b64cf507</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19566868</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1785131292</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1785348000</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2.352941</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0xb964107b4ed3c82a5366298be755f3828b8fb1fd2af25717cb4e7d5622d887fb</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.4025</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>NK CM Celje vs Egnatia Rrogozhine</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>NK CM Celje</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Egnatia Rrogozhine</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x83dfcd4e4cf4ccbab0b0d417610a39ba787c5f7b8f1d718cf691a66ab7b75964</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19557268</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1785131289</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1785262500</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2.608696</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0xbc7fd1664038aaab13393ee0f798bd8c52b9bd048ccb381842f535c2ff16718a</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.4025</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>NK CM Celje vs Egnatia Rrogozhine</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>NK CM Celje</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Egnatia Rrogozhine</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0x83dfcd4e4cf4ccbab0b0d417610a39ba787c5f7b8f1d718cf691a66ab7b75964</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19557268</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1785131236</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1785262500</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2.63354</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0xdc8c365d4440297a5a7f8b55e1846698b12d2dba8ba1ab62cce6d47978d3dfb3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.7475</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>CS U Craiova vs Levski Sofia</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>CS U Craiova</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Levski Sofia</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0xbb85e15d9520e64f7157b03d363f748b581399f6d752437afeabd985af454f2b</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19566703</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1785127689</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1785346200</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1.41806</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x0a4a13035775e455baf4c1335f4d5f222858987abf7bd69bcffd7201f2037d17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.4175</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0xe9d1eec91edb87730b0815143321f5ff812a64bbf914f9153fe49b15d31bee20</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1785127687</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2.538922</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0xa2dfa3c4170ae81c3f3fb8cb2d854d7a34035012ac510fd026df8c0cd11734a4</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Larne</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda vs Larne</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Larne</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0xb311fc0a22521012e6756f7eea2c9deaf3c0c7a458c0f3f8a6eeca6af242f43a</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19566868</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1785123433</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1785348000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>166.666667</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0x3893996e8e2400954626b7b493d53a6371a501e19f84b984e2b94e2290975ee3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.025</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Larne</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda vs Larne</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Larne</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0xb311fc0a22521012e6756f7eea2c9deaf3c0c7a458c0f3f8a6eeca6af242f43a</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19566868</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1785123384</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1785348000</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>273.2</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x522faacdbdfb0947591a8de9060cc9d6e42af2317ef1d0bd7c2736a4ccaf300d</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.5813</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty vs Omonia Nicosia</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Omonia Nicosia</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0xbb5e6a605a2ecd4d19f24de188ceddba1ae5eed0ae462e51bf0471ce737ea4b2</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19567340</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1785114214</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1785337200</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1.72043</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0xe57592777244df153e7681436f5d459adaf481d024c058813c0ea7b21c91ad5d</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.4475</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty vs Omonia Nicosia</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>FC Kairat Almaty</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Omonia Nicosia</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0xbb5e6a605a2ecd4d19f24de188ceddba1ae5eed0ae462e51bf0471ce737ea4b2</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19567340</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1785114208</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1785337200</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>11.128492</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x734515ae62c4ce1a0199ef455282df72f981caca9b505d0bc9002224672c3429</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0x237ee0a4bcC2D25604635C46468C61cfD7F51565</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.6288</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers vs FC Ararat-Armenia</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>FC Ararat-Armenia</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0x46129489d356f820281dd1c8e5155424b7ee3ba6a8a43d9377ec46399c666e47</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19583825</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1785108873</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1785265200</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1.590441</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0xf0c55f140a28591afdec7c62a9037d578e1f16619092a9d4a3f1368fd41b1baf</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.3862</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers -1</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers vs FC Ararat-Armenia</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>FC Ararat-Armenia</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x46129489d356f820281dd1c8e5155424b7ee3ba6a8a43d9377ec46399c666e47</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19583825</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1785108870</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1785265200</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>34.174757</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0xef2daa57f9c4d2d917f5d33c7896854ad6ff6ccba619fbbbcd8ddde150ca634b</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>4.99991</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.9213</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda vs Larne</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Larne</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x2d26cd20f1b572e31dc24d92bbb4220e1d8686376d97f645f5f4354b5ef9260f</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19566868</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1785100114</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1785348000</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>5.427311</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0xcdffb9ce8e11539d35b21790b78af283ee282b262c9dc1ddea860fea92e80aea</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0xbcD65d7e2D58b95Cf434eB65a82b9FD5b682D144</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>29.43</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0x6a04514e791ac06c9b873b977931340078c158c4616deb857c1431ce547fc16e</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1785100011</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>98.1</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0xdc2265546564c83ba509c9b76ea13ec72cd9b746f75f363449eaf6b931cf76fe</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>5.89999</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.6637</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda vs Larne</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Larne</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0x0b6d4b8eff4157e547fcfcccb5fb427a8295d5aff61f21193dad83ea39911992</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19566868</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1785086347</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1785348000</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>8.888874</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0xddfa64c9a530fea3862938cee1890113ad21728273eda5faeb2271ff93ea9ded</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>5.65</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.5562</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Mjallby AIF</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0x05b7cffe6c94f9c404b8a6db67d17eaf1c140c1902df42eff8a62e7778213bdc</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19577122</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1785080992</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1785254400</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>10.157303</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0x3465799d6dfa5a113f14d94d98ad8f20dce6808488c68887da6459007a8e72b9</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>54.88999</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.7675</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0xc72e785b5c22d5bd5cac40da572ce5fa136d19464978342489c467ef4bb54cf7</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1785077126</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>71.517902</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0x02ba3e85565c310cd5f304dc29915018ea4acf294d9dfd1b661f1fe4c7d02ca5</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>24.45996</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.8163</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0xf5a1f263761571306a14362e9c66386b2127c3f8c7f1e5347b97b530f1a008ad</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1785077125</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>29.96626</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0x8fca93b88bb701783ff41ab50f088e43ecef252c16331853de0b5caaf82981ce</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>16.67317</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.9525</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Gornik Zabrze vs Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Gornik Zabrze</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0x9554ca4061faee131e0027895c6052c12ffc99028dbdbdc0cbaed34b84f83d72</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19558552</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1785065229</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1785348000</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>17.50464</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0xf0e6cbd21e0194dcb37f4957b04fb677e5f7ee9f8d40616fcde455b6f5f227f6</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0xE521eC4A9c0583d53968ffe2e884E7e5Dff8880E</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.0637</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Gornik Zabrze vs Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Gornik Zabrze</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0x9554ca4061faee131e0027895c6052c12ffc99028dbdbdc0cbaed34b84f83d72</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19558552</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1785060516</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1785348000</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>59.764706</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0x353715e3f6769b2d2de1f65c261527faebaeb9af3cda531b5bb2fb93023e5e7f</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>35.88794</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.1187</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>FC Iberia 1999</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SK Slovan Bratislava vs FC Iberia 1999</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>SK Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>FC Iberia 1999</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0xaa78b65b4b857ef065f48dbcb39dcff19460b194305cbcf7f5e400377bb73e5b</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19559490</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1785059431</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1785348900</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>302.214232</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0x279b29ce10219e7b70680b5d12018ddfda7a2c4f6dd4f3a8674862ac2f090663</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>23.78</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>NK CM Celje vs Egnatia Rrogozhine</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>NK CM Celje</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Egnatia Rrogozhine</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0xf3264b5069245a4bef486698d285e492665f8fd42ce62f75db076ef0d610b3c8</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19557268</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1785056092</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1785262500</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>158.533333</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0x755e81bb5784d7b3c9e6486ea19b8ffe7212fad6e6c0cb843cb069a26e6eec88</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>72.77</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1785055626</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>132.309091</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0xe8917320e1c802fce77dabd400fa7cd1e5ef36dcfd4bf42b42bd14dbe990b3eb</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>69.73</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.375</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Mjallby AIF</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0x7c1e209322509ecf8a1b23dbc33db4cc7e79d00f2aef5b680bf0c7fff9fd4bfe</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19577122</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1785047610</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1785254400</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>185.946667</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x88e2378f5a143c7db391bb289784efb444eb47a5c1bc9793a6f9c4b6bd837f8e</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.1387</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0xebe3cd111a752d967882212fb73e0971d278b9b69d59c03364b97d883c138d02</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1785044121</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>198.414414</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0x61cde0937a84685bfdbd9e98f6a7e8a0cc4f1889f6665e9bb4792104f7ec7ea5</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.1087</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>FC Iberia 1999</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>SK Slovan Bratislava vs FC Iberia 1999</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>SK Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>FC Iberia 1999</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0xaa78b65b4b857ef065f48dbcb39dcff19460b194305cbcf7f5e400377bb73e5b</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19559490</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1785041778</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1785348900</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>31.08046</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0xb9423aefda3378641faef962e9aea7b3ce3a4217b1489c22188fbd378d6e0a13</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>132.48</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Mjallby AIF</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0x7c1e209322509ecf8a1b23dbc33db4cc7e79d00f2aef5b680bf0c7fff9fd4bfe</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19577122</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1785041402</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1785254400</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>358.054054</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0x7546990f5105879a6f4070af0c207deb23e089f9cd6d741088af685eb818e923</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0x52e769B148C8472a973EcFC9FFC0Cd8A6eE913ea</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.5725</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lech Poznan</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Lech Poznan vs Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Lech Poznan</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0x32020c9af56171026f9ca25f333b0c8fbc5c646597d73682de252484ad127d27</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19558561</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1785033197</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1785344400</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1.746725</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0xaa31bee9619141709dddf44c2b00632e6fc62aeb3e57043d7a0cfef7c1732015</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.4675</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb -1.5</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1785012663</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2.139037</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0x706deec51cdaeaab10697d88345a9605e2ae741f8edd315f86f49711040c8676</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>22.16017</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.4563</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb -1.5</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1784986094</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>48.570236</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0x818006fcbf26203fc601ff3e676bf292c22f9ba94bae860b73fd65385461ef8a</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0x1b1185C2A2d1Ec3CA592f5c21f52dD4aD449163f</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.1238</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Egnatia Rrogozhine</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>NK CM Celje vs Egnatia Rrogozhine</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>NK CM Celje</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Egnatia Rrogozhine</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0x4af948b088509c74b8501ef2371ac69aca2e07ef27aaa518441f00bee5779150</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19557268</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1784980261</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1785262500</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>72.727273</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0x665b369f4725c845e639d370e97e2cb4fe410dc123be3b585b3f180878564301</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.835</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC vs Mjallby AIF</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Mjallby AIF</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0x1899c9b65cff067e61565bfe09b869011a6687eb6d3269f60d67e143e6cd9e43</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19577122</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1784977413</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1785254400</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1.209581</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x91d87c102b052c5391dfa63fc7dcd348a62beaa901beeb8b8a768bf60fb4a5bf</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.5387</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0xbfb45a7beea984a7a9c668a058d1c5847a0afc8dae859ed584cc6881dd1e25ab</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1784900105</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>22.088167</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0x82ddad23a248269e2b8bf84351c8d266cf1f11c116b642f5d84c06741c7a0619</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.255</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Hapoel Be'er Sheva vs Víkingur Reykjavík</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Hapoel Be'er Sheva</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Víkingur Reykjavík</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0x962034a21eaa515d702829db03261f0b9ed39343dc7f36c744b170d7ebded7df</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19577307</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1784897170</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1785346200</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>18.470588</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0x8ab075f26d4fb133b3e569ea98af30f848d71683db604eab453ad0b60dca85e8</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0x34FcBC23fB24111d68542f4B3cF185543Af2fA25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.1963</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Lech Poznan vs Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Lech Poznan</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0x32b28c80c59c8961ad85019af9cdf99d3f078d598185e71cd8abb27700f16ba2</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19558561</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1784895629</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1785344400</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>37.707006</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0x76babde97bbe6342118533f3f3ad50e6e224fc6fd940aeca0e905d6733dd5175</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>43.91999</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.6225</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb -1</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb vs FC Thun</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0xe9d1eec91edb87730b0815143321f5ff812a64bbf914f9153fe49b15d31bee20</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19582472</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1784893721</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1785261600</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>70.554201</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0xee16c529f939026c958e6ddc04bce23b68a2e098ed10911de866ebc5ffd04d1e</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0x74fee38d896acdfb079a1d86f4347878d621fd4f0d8ac4b06615bc723fc48acf</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19563379</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1784890462</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1785264300</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1.801802</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0xfc0b2e1db9ca0ccfd7931bdb66c1ba6d7d6524d378b965ea8bd5bd0331f7b869</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>158.06266</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.5337</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0x74fee38d896acdfb079a1d86f4347878d621fd4f0d8ac4b06615bc723fc48acf</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19563379</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1784890461</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1785264300</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>296.136131</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0xf235c34c6db10b5456e39c6710ed412f8ffab1d22b3daa85a7ca0e19a8424b7c</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>146.89318</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.5337</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0x74fee38d896acdfb079a1d86f4347878d621fd4f0d8ac4b06615bc723fc48acf</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19563379</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1784890332</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1785264300</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>275.209705</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0x392d99c071c44b52b3d23bdf086278e82837c3330125a1e832527d6a6cabfcbb</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>16.85388</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.3875</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Champions League</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian vs SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>SK Puntigamer Sturm Graz</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0x6f059f958a714458632f78aafc6e1d15b2de9ff3fa0b4734fc30b4380a4d1054</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19563379</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1784889212</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1785264300</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>43.493884</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0x53445b69be8e1164f5c419a71c3c3a9cfd9c3aff9d05959df0e841723394a1b3</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>7.89</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Champions League_UEFA</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Lech Poznan vs Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Lech Poznan</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Aarhus AGF</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0x32b28c80c59c8961ad85019af9cdf99d3f078d598185e71cd8abb27700f16ba2</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19558561</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1784888665</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1785344400</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>36.485549</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>0x7c3fff1d3b6a87feec1182ab499530ed5f2c0c3c6518142053a93d1426386836</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
         <is>
           <t>24.56</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>1.5012</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>CS U Craiova</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Champions League_UEFA</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>CS U Craiova vs Levski Sofia</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>CS U Craiova</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>Levski Sofia</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>0xf144a86466d7bb9112d98e7107394a1b2b9e20844f05baa80656f79674578a59</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>L19566703</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
         <is>
           <t>1784888647</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>1785346200</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>48.997506</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V79" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
